--- a/data/trans_orig/P36B04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2007</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,77 +752,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5442</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>13542</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10522</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5442</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>12678</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69052</t>
+          <t>69924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104261</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58378</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91358</t>
+          <t>91214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137620</t>
+          <t>136698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184519</t>
+          <t>185248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399989</t>
+          <t>400446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>452290</t>
+          <t>452021</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395242</t>
+          <t>395859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>444935</t>
+          <t>446200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>810673</t>
+          <t>812841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>881485</t>
+          <t>882153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151261</t>
+          <t>152093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197419</t>
+          <t>196753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160478</t>
+          <t>161395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205917</t>
+          <t>206323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>325482</t>
+          <t>327426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388799</t>
+          <t>390994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19290</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97867</t>
+          <t>95701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138510</t>
+          <t>138587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54301</t>
+          <t>54523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160010</t>
+          <t>162166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214387</t>
+          <t>215327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>551587</t>
+          <t>549354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>615819</t>
+          <t>612748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>634858</t>
+          <t>634249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>693166</t>
+          <t>692383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1202188</t>
+          <t>1202006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1285901</t>
+          <t>1291010</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219969</t>
+          <t>216625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277151</t>
+          <t>270252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187283</t>
+          <t>186214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238118</t>
+          <t>238468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418331</t>
+          <t>421810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494109</t>
+          <t>498664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>54973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87209</t>
+          <t>85603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>45849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73210</t>
+          <t>75011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107471</t>
+          <t>107334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151567</t>
+          <t>151107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>378082</t>
+          <t>381985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>429549</t>
+          <t>432906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>400574</t>
+          <t>399137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>450080</t>
+          <t>451139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>791803</t>
+          <t>794584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>867610</t>
+          <t>864643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164283</t>
+          <t>163384</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>210624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159112</t>
+          <t>159072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204200</t>
+          <t>205006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>336319</t>
+          <t>335317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>400299</t>
+          <t>400192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16916</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29540</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51216</t>
+          <t>53656</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123209</t>
+          <t>125747</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167255</t>
+          <t>168079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82534</t>
+          <t>81886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217656</t>
+          <t>217903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273038</t>
+          <t>274649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>494820</t>
+          <t>490515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>550056</t>
+          <t>549774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>575659</t>
+          <t>574046</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>635666</t>
+          <t>639678</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1086164</t>
+          <t>1087280</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1174326</t>
+          <t>1172743</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208316</t>
+          <t>206245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>257022</t>
+          <t>258201</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>258692</t>
+          <t>257172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>314103</t>
+          <t>314537</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>479779</t>
+          <t>481047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>559243</t>
+          <t>558054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64228</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52532</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62991</t>
+          <t>63120</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>69288</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>108507</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>377507</t>
+          <t>376843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>450401</t>
+          <t>453484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>267929</t>
+          <t>266845</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>339252</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>666264</t>
+          <t>664443</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>767694</t>
+          <t>772591</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1883691</t>
+          <t>1880651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1991651</t>
+          <t>1999380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2053999</t>
+          <t>2060570</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2171994</t>
+          <t>2170249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3972286</t>
+          <t>3977594</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4130786</t>
+          <t>4137982</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>789136</t>
+          <t>790027</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>883569</t>
+          <t>890315</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>815609</t>
+          <t>813721</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>919337</t>
+          <t>915619</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1629731</t>
+          <t>1627085</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1770494</t>
+          <t>1771672</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35794</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64093</t>
+          <t>62499</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>77059</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>115763</t>
+          <t>115112</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2012</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55885</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>65877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100689</t>
+          <t>103375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>411637</t>
+          <t>411608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>464030</t>
+          <t>463842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>408509</t>
+          <t>407508</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460708</t>
+          <t>460815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>835135</t>
+          <t>834338</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>911212</t>
+          <t>909157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184495</t>
+          <t>184695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232132</t>
+          <t>232857</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>177031</t>
+          <t>178045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226214</t>
+          <t>225785</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373664</t>
+          <t>374353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443763</t>
+          <t>445348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23729</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>35816</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>60288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>96455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73035</t>
+          <t>73446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111336</t>
+          <t>111244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140584</t>
+          <t>139903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191748</t>
+          <t>190863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>595782</t>
+          <t>593906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660129</t>
+          <t>662034</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>597357</t>
+          <t>593253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>664361</t>
+          <t>659019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210753</t>
+          <t>1210692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304789</t>
+          <t>1299412</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252980</t>
+          <t>254041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311955</t>
+          <t>315813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>235088</t>
+          <t>235328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>290853</t>
+          <t>291299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505229</t>
+          <t>507302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>588296</t>
+          <t>586788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26890</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52750</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42107</t>
+          <t>43144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>72664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8679</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76497</t>
+          <t>74221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113679</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>76281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112855</t>
+          <t>112433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>159605</t>
+          <t>160752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213100</t>
+          <t>214345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>459549</t>
+          <t>463354</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514863</t>
+          <t>515619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>478020</t>
+          <t>479867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534476</t>
+          <t>533247</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>957598</t>
+          <t>956936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1037465</t>
+          <t>1035703</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119125</t>
+          <t>119746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>164284</t>
+          <t>162766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109123</t>
+          <t>111956</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152346</t>
+          <t>152504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238626</t>
+          <t>241847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304670</t>
+          <t>302429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>28349</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36413</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55658</t>
+          <t>55057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26376</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35017</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63663</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>57614</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>89966</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69321</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104639</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133842</t>
+          <t>136695</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>184470</t>
+          <t>185224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>499438</t>
+          <t>504762</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>564395</t>
+          <t>564742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>563931</t>
+          <t>561241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>630280</t>
+          <t>628519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1084200</t>
+          <t>1084126</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1177348</t>
+          <t>1172366</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,84%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>261104</t>
+          <t>260677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>319399</t>
+          <t>320068</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274471</t>
+          <t>274756</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>337756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>554144</t>
+          <t>555879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>642010</t>
+          <t>638087</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41982</t>
+          <t>42676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45431</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79118</t>
+          <t>76513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>62935</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47804</t>
+          <t>48318</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80507</t>
+          <t>81644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89840</t>
+          <t>88707</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132924</t>
+          <t>132862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>249117</t>
+          <t>248758</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>316880</t>
+          <t>313126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>280542</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>349039</t>
+          <t>350818</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>548122</t>
+          <t>548788</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>641885</t>
+          <t>641765</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2036020</t>
+          <t>2028442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2148960</t>
+          <t>2148819</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2111183</t>
+          <t>2108182</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2229957</t>
+          <t>2226672</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4176699</t>
+          <t>4168795</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4340834</t>
+          <t>4337596</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>864210</t>
+          <t>866813</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>972814</t>
+          <t>979150</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>847378</t>
+          <t>843368</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>952022</t>
+          <t>952715</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1751930</t>
+          <t>1747458</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1897699</t>
+          <t>1899901</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>99201</t>
+          <t>100394</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>82263</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>123585</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>154387</t>
+          <t>153249</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>207110</t>
+          <t>209759</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2016</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>59148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92047</t>
+          <t>93763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51970</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118274</t>
+          <t>118442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>164307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346166</t>
+          <t>343852</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>397186</t>
+          <t>395750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>351283</t>
+          <t>351576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>402136</t>
+          <t>402315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>708676</t>
+          <t>712531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>782087</t>
+          <t>784500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181795</t>
+          <t>184547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227781</t>
+          <t>232057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182393</t>
+          <t>181053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231837</t>
+          <t>229797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377322</t>
+          <t>377480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445182</t>
+          <t>443801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>38103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83805</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124918</t>
+          <t>124844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73465</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167270</t>
+          <t>167433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221288</t>
+          <t>222420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>551900</t>
+          <t>552228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617356</t>
+          <t>616181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>561660</t>
+          <t>562097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>627267</t>
+          <t>629651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1138450</t>
+          <t>1139045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1228381</t>
+          <t>1227295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>283999</t>
+          <t>283800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346151</t>
+          <t>343076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290795</t>
+          <t>286264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353374</t>
+          <t>349884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>587506</t>
+          <t>591486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>673303</t>
+          <t>673684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48333</t>
+          <t>48437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>44677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47568</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>79604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>70650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103847</t>
+          <t>105497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127315</t>
+          <t>125616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171866</t>
+          <t>173024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>329001</t>
+          <t>328439</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>385427</t>
+          <t>385596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>340070</t>
+          <t>341413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>397308</t>
+          <t>399443</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>690776</t>
+          <t>690626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>765288</t>
+          <t>768559</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>259678</t>
+          <t>254891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313817</t>
+          <t>312026</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>248885</t>
+          <t>250799</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305088</t>
+          <t>305244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>522076</t>
+          <t>521687</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>595098</t>
+          <t>602215</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22594</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>47096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53823</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>88801</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>34630</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19876</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41805</t>
+          <t>42745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>84526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>124520</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87019</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127833</t>
+          <t>130541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>183334</t>
+          <t>179629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>238648</t>
+          <t>239998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>517302</t>
+          <t>519289</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>578171</t>
+          <t>580408</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>562304</t>
+          <t>562498</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>628192</t>
+          <t>630916</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1101347</t>
+          <t>1101361</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1189617</t>
+          <t>1193390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>235683</t>
+          <t>236250</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288715</t>
+          <t>286413</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274449</t>
+          <t>269015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>333520</t>
+          <t>330592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>516393</t>
+          <t>523082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>600737</t>
+          <t>606107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23890</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46341</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>41699</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>72886</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71703</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>109997</t>
+          <t>109281</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>308365</t>
+          <t>307958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>379583</t>
+          <t>380176</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>312062</t>
+          <t>312818</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>382902</t>
+          <t>386689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>639344</t>
+          <t>642101</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>742007</t>
+          <t>746396</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1802266</t>
+          <t>1803729</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1921966</t>
+          <t>1918901</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1879344</t>
+          <t>1873014</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1998573</t>
+          <t>2000911</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3719787</t>
+          <t>3717651</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3884502</t>
+          <t>3889140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1009133</t>
+          <t>1012073</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1118314</t>
+          <t>1118844</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1051973</t>
+          <t>1044905</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1158760</t>
+          <t>1161574</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2092627</t>
+          <t>2091058</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2243743</t>
+          <t>2245270</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>95169</t>
+          <t>96398</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67185</t>
+          <t>66851</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>104607</t>
+          <t>103431</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136551</t>
+          <t>134505</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>188332</t>
+          <t>185900</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69924</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106204</t>
+          <t>104496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58768</t>
+          <t>59830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91214</t>
+          <t>91378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136698</t>
+          <t>136830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185248</t>
+          <t>183506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>400446</t>
+          <t>395887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>452021</t>
+          <t>450939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>395859</t>
+          <t>395595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446200</t>
+          <t>444603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>812841</t>
+          <t>813024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>882153</t>
+          <t>882997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152093</t>
+          <t>152464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196753</t>
+          <t>198243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161395</t>
+          <t>160548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206323</t>
+          <t>205539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327426</t>
+          <t>329543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>390994</t>
+          <t>391035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95701</t>
+          <t>96645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138587</t>
+          <t>139562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>54319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>86501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162166</t>
+          <t>161211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215327</t>
+          <t>215435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>549354</t>
+          <t>549804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>612748</t>
+          <t>611639</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>634249</t>
+          <t>632451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>692383</t>
+          <t>690768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1202006</t>
+          <t>1201850</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291010</t>
+          <t>1285155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216625</t>
+          <t>217868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>270252</t>
+          <t>270505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186214</t>
+          <t>186895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238468</t>
+          <t>237247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>421810</t>
+          <t>419428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>496350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29443</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54973</t>
+          <t>54778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85603</t>
+          <t>88101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45849</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75011</t>
+          <t>75563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107334</t>
+          <t>108974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151107</t>
+          <t>150610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>381985</t>
+          <t>379784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>432906</t>
+          <t>430665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>399137</t>
+          <t>399835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>451139</t>
+          <t>449888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>794584</t>
+          <t>790429</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>864643</t>
+          <t>863773</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>163384</t>
+          <t>163260</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>211964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>159119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205006</t>
+          <t>205391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>335317</t>
+          <t>335616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>400192</t>
+          <t>403131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>29478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53656</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125747</t>
+          <t>123436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168079</t>
+          <t>167818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81886</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121901</t>
+          <t>120078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217903</t>
+          <t>213957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274649</t>
+          <t>273726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>490515</t>
+          <t>493317</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>549774</t>
+          <t>553326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>574046</t>
+          <t>576062</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>639678</t>
+          <t>638359</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1087280</t>
+          <t>1085539</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1172743</t>
+          <t>1172363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>206245</t>
+          <t>207252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258201</t>
+          <t>258283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>257172</t>
+          <t>259667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>314537</t>
+          <t>318048</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>481047</t>
+          <t>482675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>558054</t>
+          <t>559397</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>37554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15674</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>36939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65276</t>
+          <t>63907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>85707</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>68418</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>106181</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>85707</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>69288</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>105400</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>376843</t>
+          <t>379548</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>453484</t>
+          <t>456868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>266845</t>
+          <t>270576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>339202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>664443</t>
+          <t>670329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>772591</t>
+          <t>770317</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1880651</t>
+          <t>1879227</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1999380</t>
+          <t>1996366</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2060570</t>
+          <t>2055617</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2170249</t>
+          <t>2168400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3977594</t>
+          <t>3970636</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4137982</t>
+          <t>4130882</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>790027</t>
+          <t>784171</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>890315</t>
+          <t>885117</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>813721</t>
+          <t>815608</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>915619</t>
+          <t>916465</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1627085</t>
+          <t>1622078</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1771672</t>
+          <t>1772027</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>35576</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>77619</t>
+          <t>76847</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>115112</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57088</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31933</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59495</t>
+          <t>58036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103375</t>
+          <t>103332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>411608</t>
+          <t>409262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>463842</t>
+          <t>464525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>407508</t>
+          <t>409086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460815</t>
+          <t>461136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>834338</t>
+          <t>835939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>909157</t>
+          <t>911608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184695</t>
+          <t>184915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232857</t>
+          <t>236729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178045</t>
+          <t>175438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225785</t>
+          <t>224622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>374353</t>
+          <t>375694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445348</t>
+          <t>447551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35816</t>
+          <t>34858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96455</t>
+          <t>94086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73446</t>
+          <t>74021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111244</t>
+          <t>111114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139903</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190863</t>
+          <t>191387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>593906</t>
+          <t>595281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>662034</t>
+          <t>658580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>593253</t>
+          <t>594451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659019</t>
+          <t>657845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210692</t>
+          <t>1209922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1299412</t>
+          <t>1299688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,56%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>254041</t>
+          <t>251619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315813</t>
+          <t>312672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>235328</t>
+          <t>232011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291299</t>
+          <t>290206</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507302</t>
+          <t>502073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>586788</t>
+          <t>587922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51894</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43144</t>
+          <t>41505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72664</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>25548</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>74329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113895</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76281</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112433</t>
+          <t>114855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>160752</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214345</t>
+          <t>212974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>463354</t>
+          <t>459584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>515619</t>
+          <t>519181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479867</t>
+          <t>478951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>533247</t>
+          <t>534636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>956936</t>
+          <t>958931</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1035703</t>
+          <t>1032822</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>120405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162766</t>
+          <t>165554</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111956</t>
+          <t>110372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152504</t>
+          <t>154261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>241847</t>
+          <t>241255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302429</t>
+          <t>305460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>57720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>34400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57614</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89966</t>
+          <t>91613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68709</t>
+          <t>69458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>105044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136695</t>
+          <t>135145</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185224</t>
+          <t>185450</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>504762</t>
+          <t>506203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>564742</t>
+          <t>569728</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>561241</t>
+          <t>562130</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>628519</t>
+          <t>627361</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1084126</t>
+          <t>1079916</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1172366</t>
+          <t>1175178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>260677</t>
+          <t>259117</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>320068</t>
+          <t>316673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274756</t>
+          <t>278705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>337756</t>
+          <t>340058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>555879</t>
+          <t>555967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>638087</t>
+          <t>636738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48318</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>81644</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88707</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132862</t>
+          <t>136218</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>248758</t>
+          <t>249318</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>313126</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>279149</t>
+          <t>277534</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>350818</t>
+          <t>346838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>548788</t>
+          <t>548108</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>641765</t>
+          <t>641718</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2028442</t>
+          <t>2028767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2148819</t>
+          <t>2148905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2108182</t>
+          <t>2107248</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2226672</t>
+          <t>2228508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4168795</t>
+          <t>4179214</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4337596</t>
+          <t>4349538</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>866813</t>
+          <t>870380</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>979150</t>
+          <t>976128</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>843368</t>
+          <t>849346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>952715</t>
+          <t>953425</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1747458</t>
+          <t>1740312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1899901</t>
+          <t>1892004</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>99944</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>82263</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>123585</t>
+          <t>124828</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>153249</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>209759</t>
+          <t>209931</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>58961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93763</t>
+          <t>92223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53640</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83303</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118442</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164307</t>
+          <t>164299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343852</t>
+          <t>344470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395750</t>
+          <t>397875</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>351576</t>
+          <t>352528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>402315</t>
+          <t>403971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>712531</t>
+          <t>706344</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>784500</t>
+          <t>784408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184547</t>
+          <t>179086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232057</t>
+          <t>227802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181053</t>
+          <t>178630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229797</t>
+          <t>228671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377480</t>
+          <t>377776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443801</t>
+          <t>445392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>36520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>84192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124844</t>
+          <t>124227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72946</t>
+          <t>73003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>109985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167433</t>
+          <t>167711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>222420</t>
+          <t>220096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>552228</t>
+          <t>551026</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616181</t>
+          <t>615637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>562097</t>
+          <t>561645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>629651</t>
+          <t>627003</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1139045</t>
+          <t>1131095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1227295</t>
+          <t>1224945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>283800</t>
+          <t>286242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>343076</t>
+          <t>347317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>286264</t>
+          <t>290682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349884</t>
+          <t>350995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>591486</t>
+          <t>594805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>673684</t>
+          <t>678969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48437</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47203</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79604</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70650</t>
+          <t>70343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105497</t>
+          <t>104937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125616</t>
+          <t>127027</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173024</t>
+          <t>176135</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>328439</t>
+          <t>329976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>385596</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>341413</t>
+          <t>340719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>399443</t>
+          <t>399181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>690626</t>
+          <t>686542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>768559</t>
+          <t>769702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>254891</t>
+          <t>258488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312026</t>
+          <t>315681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>250799</t>
+          <t>249145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>305244</t>
+          <t>306520</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>521687</t>
+          <t>523582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>602215</t>
+          <t>600782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47096</t>
+          <t>46856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>53913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88801</t>
+          <t>88079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34630</t>
+          <t>34478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84526</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124520</t>
+          <t>123897</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87345</t>
+          <t>88179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>130541</t>
+          <t>131205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179629</t>
+          <t>179757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239998</t>
+          <t>234160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>519289</t>
+          <t>519176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>580408</t>
+          <t>579454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>562498</t>
+          <t>565602</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>630916</t>
+          <t>630630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1101361</t>
+          <t>1101367</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1193390</t>
+          <t>1192030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>236250</t>
+          <t>236009</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>287650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>269015</t>
+          <t>271325</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330592</t>
+          <t>331836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519581</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>606107</t>
+          <t>604235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>47340</t>
+          <t>46694</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>41381</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72886</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>72344</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>111332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>307958</t>
+          <t>307173</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>380176</t>
+          <t>380843</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>312818</t>
+          <t>315072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>386689</t>
+          <t>388412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>642101</t>
+          <t>637700</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>746396</t>
+          <t>742607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1803729</t>
+          <t>1806014</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1918901</t>
+          <t>1926222</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1873014</t>
+          <t>1877919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2000911</t>
+          <t>2004598</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3717651</t>
+          <t>3728822</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3889140</t>
+          <t>3892331</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1012073</t>
+          <t>1003959</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1118844</t>
+          <t>1120440</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1044905</t>
+          <t>1043206</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1161574</t>
+          <t>1159089</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2091058</t>
+          <t>2089719</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2245270</t>
+          <t>2241299</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>61314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66851</t>
+          <t>66285</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>103431</t>
+          <t>103914</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134505</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185900</t>
+          <t>184777</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
